--- a/analysis/constellation-software/history-2007-2025/history_metrics.xlsx
+++ b/analysis/constellation-software/history-2007-2025/history_metrics.xlsx
@@ -648,6 +648,9 @@
       <c r="L7" t="n">
         <v>8.119999999999999</v>
       </c>
+      <c r="M7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -808,21 +811,39 @@
       <c r="D11" t="n">
         <v>9.73</v>
       </c>
+      <c r="E11" t="n">
+        <v>23.1</v>
+      </c>
       <c r="F11" t="n">
         <v>18.59</v>
       </c>
+      <c r="G11" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="H11" t="n">
+        <v>36.27</v>
+      </c>
       <c r="I11" t="n">
         <v>45.09</v>
       </c>
       <c r="J11" t="n">
         <v>100.29</v>
       </c>
+      <c r="K11" t="n">
+        <v>23.17</v>
+      </c>
       <c r="L11" t="n">
         <v>18.64</v>
       </c>
+      <c r="M11" t="n">
+        <v>4</v>
+      </c>
       <c r="N11" t="n">
         <v>216.9</v>
       </c>
+      <c r="O11" t="n">
+        <v>132.14</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -857,6 +878,9 @@
       <c r="L12" t="n">
         <v>21.85</v>
       </c>
+      <c r="M12" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1035,9 +1059,15 @@
       <c r="L16" t="n">
         <v>41.67</v>
       </c>
+      <c r="M16" t="n">
+        <v>4</v>
+      </c>
       <c r="N16" t="n">
         <v>-454</v>
       </c>
+      <c r="O16" t="n">
+        <v>-538.76</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1051,14 +1081,26 @@
       <c r="D17" t="n">
         <v>7.73</v>
       </c>
+      <c r="E17" t="n">
+        <v>19.59</v>
+      </c>
       <c r="F17" t="n">
         <v>12.88</v>
       </c>
+      <c r="G17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="H17" t="n">
+        <v>123.36</v>
+      </c>
       <c r="I17" t="n">
         <v>187.57</v>
       </c>
       <c r="J17" t="n">
         <v>312.51</v>
+      </c>
+      <c r="K17" t="n">
+        <v>61.21</v>
       </c>
       <c r="L17" t="n">
         <v>40.25</v>
@@ -1222,7 +1264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1610,6 +1652,60 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>acquisition_count</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>['https://tracxn.com/d/acquisitions/acquisitions-by-constellation-software/__YaRluimuGqgVfqr0Xhgb2dPWiMKnmgzXPcPNPni5Ssg']</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Set to gap by Fable review 2026-09-14: the figure counts publicly announced major deals, not the company's total for FY2015; Constellation closes dozens of small acquisitions a year, so 3 is not a total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>acquisition_count</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>['https://nicoper.substack.com/p/4-constellation-acquisitions-2022']</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Set to gap by Fable review 2026-09-14: the figure counts publicly announced major deals, not the company's total for FY2019; Constellation closes dozens of small acquisitions a year, so 3 is not a total.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1621,7 +1717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G192"/>
+  <dimension ref="A1:G198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5496,16 +5592,16 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>fcfa2s</t>
+          <t>cash_from_operations</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>FY2018</t>
+          <t>FY2016</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>559</v>
+        <v>491</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -5519,28 +5615,28 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2020/02/13/1984977/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2019-and-Declares-Quarterly-Dividend.html</t>
+          <t>https://www.globenewswire.com/news-release/2018/02/14/1348408/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2017-and-Declares-Quarterly-Dividend.html</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Reused from long-term-hold/holdings.json parent_long_run.</t>
+          <t>Comparative figure stated in the FY2017 annual release ('increase of 8%/$37M over $491M in 2016'). Added by Fable review 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>fcfa2s</t>
+          <t>cash_from_operations</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>FY2019</t>
+          <t>FY2022</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>590</v>
+        <v>1297</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -5554,12 +5650,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2020/02/13/1984977/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2019-and-Declares-Quarterly-Dividend.html</t>
+          <t>https://www.globenewswire.com/news-release/2023/03/29/2637195/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2022-and-Declares-Quarterly-Dividend.html</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Reused from parent_long_run. 6% increase over FY2018.</t>
+          <t>Release states CFO of $1,297 million for 2022, a decrease of $2 million from $1,300 million in 2021. Added by Fable review 2026-09-14 from a WebSearch snippet.</t>
         </is>
       </c>
     </row>
@@ -5571,11 +5667,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>FY2020</t>
+          <t>FY2018</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>989</v>
+        <v>559</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -5589,12 +5685,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2021/02/12/2175170/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2020-and-Declares-Quarterly-Dividend.html</t>
+          <t>https://www.globenewswire.com/news-release/2020/02/13/1984977/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2019-and-Declares-Quarterly-Dividend.html</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Reused from parent_long_run. +68%/$399M over FY2019.</t>
+          <t>Reused from long-term-hold/holdings.json parent_long_run.</t>
         </is>
       </c>
     </row>
@@ -5606,11 +5702,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2019</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>883</v>
+        <v>590</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -5624,12 +5720,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2022/02/10/2383319/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2021-and-Declares-Quarterly-Dividend.html</t>
+          <t>https://www.globenewswire.com/news-release/2020/02/13/1984977/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2019-and-Declares-Quarterly-Dividend.html</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Reused from parent_long_run. -11%/$106M vs FY2020, mainly the TSS/IRGA revaluation charge and Topicus.com non-controlling interests.</t>
+          <t>Reused from parent_long_run. 6% increase over FY2018.</t>
         </is>
       </c>
     </row>
@@ -5641,11 +5737,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2020</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>853</v>
+        <v>989</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -5659,12 +5755,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.csisoftware.com/docs/default-source/investor-relations/statutory-filings/csi---mda-q4-2023---final.pdf?sfvrsn=47d7de81_3</t>
+          <t>https://www.globenewswire.com/news-release/2021/02/12/2175170/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2020-and-Declares-Quarterly-Dividend.html</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Reused from ledger.json.</t>
+          <t>Reused from parent_long_run. +68%/$399M over FY2019.</t>
         </is>
       </c>
     </row>
@@ -5676,11 +5772,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2021</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1160</v>
+        <v>883</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -5694,12 +5790,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2024/03/06/2841834/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2023-and-Declares-Quarterly-Dividend.html</t>
+          <t>https://www.globenewswire.com/news-release/2022/02/10/2383319/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2021-and-Declares-Quarterly-Dividend.html</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Reused from ledger.json.</t>
+          <t>Reused from parent_long_run. -11%/$106M vs FY2020, mainly the TSS/IRGA revaluation charge and Topicus.com non-controlling interests.</t>
         </is>
       </c>
     </row>
@@ -5711,11 +5807,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2022</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1472</v>
+        <v>853</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -5729,7 +5825,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.csisoftware.com/constellation-software-inc-announces-results-for-the-fourth-quarter-and-year-ended-december-31-2024-and-declares-quarterly-dividend/</t>
+          <t>https://www.csisoftware.com/docs/default-source/investor-relations/statutory-filings/csi---mda-q4-2023---final.pdf?sfvrsn=47d7de81_3</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -5746,11 +5842,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1683</v>
+        <v>1160</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -5764,32 +5860,32 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/03/09/3251696/0/en/constellation-software-inc-announces-results-for-the-fourth-quarter-and-year-ended-december-31-2025-and-declares-quarterly-dividend.html</t>
+          <t>https://www.globenewswire.com/news-release/2024/03/06/2841834/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2023-and-Declares-Quarterly-Dividend.html</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Reused from ledger.json. +$210M/14% over FY2024's $1,472M.</t>
+          <t>Reused from ledger.json.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>acquisitions_cash_spent</t>
+          <t>fcfa2s</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>FY2008</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>94</v>
+        <v>1472</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>USD millions approximate</t>
+          <t>USD millions</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -5799,28 +5895,28 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.mbi-deepdives.com/content/files/2022/07/Constellation-Software-SH-Letters-Merged.pdf</t>
+          <t>https://www.csisoftware.com/constellation-software-inc-announces-results-for-the-fourth-quarter-and-year-ended-december-31-2024-and-declares-quarterly-dividend/</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2008 President's letter: ~$94M of capital deployed/committed in 2008 (Maximus assets, 16 other businesses, VMS share purchases, pending Gladstone plc offer). This is total capital deployed/committed, not strictly cash spent on closed acquisitions.</t>
+          <t>Reused from ledger.json.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>acquisitions_cash_spent</t>
+          <t>fcfa2s</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>FY2013</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>558</v>
+        <v>1683</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -5834,12 +5930,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1113678/000119312514275886/d757774dex21.htm</t>
+          <t>https://www.globenewswire.com/news-release/2026/03/09/3251696/0/en/constellation-software-inc-announces-results-for-the-fourth-quarter-and-year-ended-december-31-2025-and-declares-quarterly-dividend.html</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Thirty acquisitions for aggregate cash consideration of $558M (plus $27M holdbacks and $4M contingent consideration, not included). Includes the TSS acquisition, closed Dec 31, 2013.</t>
+          <t>Reused from ledger.json. +$210M/14% over FY2024's $1,472M.</t>
         </is>
       </c>
     </row>
@@ -5851,15 +5947,15 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>FY2014</t>
+          <t>FY2008</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>USD millions</t>
+          <t>USD millions approximate</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -5869,12 +5965,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1113678/000119312515138334/d906182dex26.htm</t>
+          <t>https://www.mbi-deepdives.com/content/files/2022/07/Constellation-Software-SH-Letters-Merged.pdf</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>23 acquisitions for aggregate cash consideration of $115M (plus $17M holdbacks, $8M contingent consideration, not included).</t>
+          <t>2008 President's letter: ~$94M of capital deployed/committed in 2008 (Maximus assets, 16 other businesses, VMS share purchases, pending Gladstone plc offer). This is total capital deployed/committed, not strictly cash spent on closed acquisitions.</t>
         </is>
       </c>
     </row>
@@ -5886,11 +5982,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>FY2015</t>
+          <t>FY2013</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>248.8</v>
+        <v>558</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -5904,12 +6000,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.csisoftware.com/docs/default-source/investor-relations/statutory-filings/sr_q4_2015.pdf</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1113678/000119312514275886/d757774dex21.htm</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Aggregate of $248.8M, including holdback payments on prior acquisitions -- not directly comparable line-for-line with the FY2013/FY2014 figures above.</t>
+          <t>Thirty acquisitions for aggregate cash consideration of $558M (plus $27M holdbacks and $4M contingent consideration, not included). Includes the TSS acquisition, closed Dec 31, 2013.</t>
         </is>
       </c>
     </row>
@@ -5921,11 +6017,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>FY2016</t>
+          <t>FY2014</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>178.1</v>
+        <v>115</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -5939,12 +6035,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.csisoftware.com/docs/default-source/investor-relations/statutory-filings/mda_q4_2016.pdf</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1113678/000119312515138334/d906182dex26.htm</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Reused from long-term-hold/holdings.json parent_long_run (mda_q4_2016.pdf). This project's own FY2012-2016 intake sweep did not locate this figure and recorded it as a gap; parent_long_run already held it.</t>
+          <t>23 acquisitions for aggregate cash consideration of $115M (plus $17M holdbacks, $8M contingent consideration, not included).</t>
         </is>
       </c>
     </row>
@@ -5956,11 +6052,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>FY2018</t>
+          <t>FY2015</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>603</v>
+        <v>248.8</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -5974,10 +6070,14 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2019/02/14/1725078/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2018-and-Declares-Quarterly-and-Special-Dividends.html</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr"/>
+          <t>https://www.csisoftware.com/docs/default-source/investor-relations/statutory-filings/sr_q4_2015.pdf</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Aggregate of $248.8M, including holdback payments on prior acquisitions -- not directly comparable line-for-line with the FY2013/FY2014 figures above.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5987,15 +6087,15 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>FY2019</t>
+          <t>FY2016</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>688</v>
+        <v>178.1</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>USD millions, total consideration</t>
+          <t>USD millions</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -6005,12 +6105,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2020/02/13/1984977/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2019-and-Declares-Quarterly-Dividend.html</t>
+          <t>https://www.csisoftware.com/docs/default-source/investor-relations/statutory-filings/mda_q4_2016.pdf</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>'Completed acquisitions totaling $688 million in consideration during 2019', directly quoted from the FY2019 release. A $549M 'aggregate cash consideration including acquired cash' figure sourced to the 2019 AIF (confidence third_party in this project's intake, and used in parent_long_run) is recorded as a conflict; the company-quoted $688M total-consideration figure is preferred.</t>
+          <t>Reused from long-term-hold/holdings.json parent_long_run (mda_q4_2016.pdf). This project's own FY2012-2016 intake sweep did not locate this figure and recorded it as a gap; parent_long_run already held it.</t>
         </is>
       </c>
     </row>
@@ -6022,32 +6122,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>FY2020</t>
+          <t>FY2018</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>179</v>
+        <v>603</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>USD millions, aggregate cash consideration including acquired cash</t>
+          <t>USD millions</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>third_party</t>
+          <t>company</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2021/02/12/2175170/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2020-and-Declares-Quarterly-Dividend.html</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>WebSearch summary attributed this to FY2020 disclosures but did not quote it directly from the release text; no company-confirmed figure was found for FY2020. Matches parent_long_run and ledger.json.</t>
-        </is>
-      </c>
+          <t>https://www.globenewswire.com/news-release/2019/02/14/1725078/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2018-and-Declares-Quarterly-and-Special-Dividends.html</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6057,15 +6153,15 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2019</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1337</v>
+        <v>688</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>USD millions, aggregate including holdback payments, net of a $33M additional subscription related to Topicus.com B.V.</t>
+          <t>USD millions, total consideration</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -6075,12 +6171,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.csisoftware.com/docs/default-source/press-releases/csi---mda-q4-2021---final.pdf</t>
+          <t>https://www.globenewswire.com/news-release/2020/02/13/1984977/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2019-and-Declares-Quarterly-Dividend.html</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Reused from parent_long_run (Q4 2021 MD&amp;A). A separate company-sourced $1,517M 'total consideration including holdbacks, contingent consideration and amounts related to Topicus.com B.V.' figure was found independently in this project's own FY2021 release search and is recorded as a conflict (net vs. total consideration are different bases).</t>
+          <t>'Completed acquisitions totaling $688 million in consideration during 2019', directly quoted from the FY2019 release. A $549M 'aggregate cash consideration including acquired cash' figure sourced to the 2019 AIF (confidence third_party in this project's intake, and used in parent_long_run) is recorded as a conflict; the company-quoted $688M total-consideration figure is preferred.</t>
         </is>
       </c>
     </row>
@@ -6092,15 +6188,15 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2020</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1600</v>
+        <v>179</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>USD millions</t>
+          <t>USD millions, aggregate cash consideration including acquired cash</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -6110,12 +6206,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.speedwellmemos.com/p/constellation-software-2022-earnings</t>
+          <t>https://www.globenewswire.com/news-release/2021/02/12/2175170/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2020-and-Declares-Quarterly-Dividend.html</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>No company-disclosed aggregate acquisition spend was found for FY2022; matches ledger.json and parent_long_run, all citing the same third-party source.</t>
+          <t>WebSearch summary attributed this to FY2020 disclosures but did not quote it directly from the release text; no company-confirmed figure was found for FY2020. Matches parent_long_run and ledger.json.</t>
         </is>
       </c>
     </row>
@@ -6127,15 +6223,15 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2021</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>732</v>
+        <v>1337</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>USD millions</t>
+          <t>USD millions, aggregate including holdback payments, net of a $33M additional subscription related to Topicus.com B.V.</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -6145,10 +6241,14 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2024/03/06/2841834/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2023-and-Declares-Quarterly-Dividend.html</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr"/>
+          <t>https://www.csisoftware.com/docs/default-source/press-releases/csi---mda-q4-2021---final.pdf</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Reused from parent_long_run (Q4 2021 MD&amp;A). A separate company-sourced $1,517M 'total consideration including holdbacks, contingent consideration and amounts related to Topicus.com B.V.' figure was found independently in this project's own FY2021 release search and is recorded as a conflict (net vs. total consideration are different bases).</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6158,11 +6258,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2022</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1792</v>
+        <v>1600</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -6171,15 +6271,19 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2025/03/07/3039269/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2024-and-Declares-Quarterly-Dividend.html</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr"/>
+          <t>https://www.speedwellmemos.com/p/constellation-software-2022-earnings</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>No company-disclosed aggregate acquisition spend was found for FY2022; matches ledger.json and parent_long_run, all citing the same third-party source.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6189,11 +6293,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1579</v>
+        <v>732</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -6207,32 +6311,28 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/03/09/3251696/0/en/constellation-software-inc-announces-results-for-the-fourth-quarter-and-year-ended-december-31-2025-and-declares-quarterly-dividend.html</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Total acquisition consideration of $1,579M including holdbacks and contingent consideration.</t>
-        </is>
-      </c>
+          <t>https://www.globenewswire.com/news-release/2024/03/06/2841834/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2023-and-Declares-Quarterly-Dividend.html</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>acquisition_count</t>
+          <t>acquisitions_cash_spent</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>FY2008</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>17</v>
+        <v>1792</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>count approximate</t>
+          <t>USD millions</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -6242,47 +6342,43 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.mbi-deepdives.com/content/files/2022/07/Constellation-Software-SH-Letters-Merged.pdf</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>2008 letter: 'bought the Maximus assets and 16 other businesses' -&gt; 1 + 16 = 17.</t>
-        </is>
-      </c>
+          <t>https://www.globenewswire.com/news-release/2025/03/07/3039269/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2024-and-Declares-Quarterly-Dividend.html</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>acquisition_count</t>
+          <t>acquisitions_cash_spent</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>FY2012</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>35</v>
+        <v>1579</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>USD millions</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>company</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1113678/000119312515138334/d906182dex26.htm</t>
+          <t>https://www.globenewswire.com/news-release/2026/03/09/3251696/0/en/constellation-software-inc-announces-results-for-the-fourth-quarter-and-year-ended-december-31-2025-and-declares-quarterly-dividend.html</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Derived from a comparative sentence in the FY2013 disclosure ('thirty acquisitions... compared to thirty-five in 2012'); no primary FY2012 release figure found.</t>
+          <t>Total acquisition consideration of $1,579M including holdbacks and contingent consideration.</t>
         </is>
       </c>
     </row>
@@ -6294,15 +6390,15 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>FY2013</t>
+          <t>FY2008</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>count approximate</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -6312,10 +6408,14 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1113678/000119312514275886/d757774dex21.htm</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr"/>
+          <t>https://www.mbi-deepdives.com/content/files/2022/07/Constellation-Software-SH-Letters-Merged.pdf</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2008 letter: 'bought the Maximus assets and 16 other businesses' -&gt; 1 + 16 = 17.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6325,11 +6425,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>FY2014</t>
+          <t>FY2012</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -6338,7 +6438,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6348,7 +6448,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lower than FY2013's 30; the intake's 'record year' framing for FY2014 acquisitions was not corroborated on a count or cash-consideration basis.</t>
+          <t>Derived from a comparative sentence in the FY2013 disclosure ('thirty acquisitions... compared to thirty-five in 2012'); no primary FY2012 release figure found.</t>
         </is>
       </c>
     </row>
@@ -6360,11 +6460,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>FY2015</t>
+          <t>FY2013</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -6373,19 +6473,15 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>third_party</t>
+          <t>company</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://tracxn.com/d/acquisitions/acquisitions-by-constellation-software/__YaRluimuGqgVfqr0Xhgb2dPWiMKnmgzXPcPNPni5Ssg</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>Low-confidence third-party M&amp;A database count; implausibly low vs. the company's typical pace elsewhere in this window. Matches parent_long_run.</t>
-        </is>
-      </c>
+          <t>https://www.sec.gov/Archives/edgar/data/1113678/000119312514275886/d757774dex21.htm</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6395,11 +6491,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>FY2019</t>
+          <t>FY2014</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -6408,17 +6504,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>third_party</t>
+          <t>company</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://nicoper.substack.com/p/4-constellation-acquisitions-2022</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1113678/000119312515138334/d906182dex26.htm</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Third-party count; matches parent_long_run.</t>
+          <t>Lower than FY2013's 30; the intake's 'record year' framing for FY2014 acquisitions was not corroborated on a count or cash-consideration basis.</t>
         </is>
       </c>
     </row>
@@ -6430,85 +6526,79 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>85</v>
+          <t>FY2015</t>
+        </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>count approximate, company-wide, stated as a minimum ('more than')</t>
+          <t>count</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>third_party</t>
+          <t>unreliable</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://explore.volarisgroup.com/volaris-group-blog/volaris-recognized-as-a-top-acquirer</t>
+          <t>https://tracxn.com/d/acquisitions/acquisitions-by-constellation-software/__YaRluimuGqgVfqr0Xhgb2dPWiMKnmgzXPcPNPni5Ssg</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Third-party (Volaris/Corum Group) reporting; not a Constellation-disclosed figure.</t>
+          <t>Low-confidence third-party M&amp;A database count; implausibly low vs. the company's typical pace elsewhere in this window. Matches parent_long_run. Set to gap: counts disclosed major deals only, not the annual total.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>shares_outstanding</t>
+          <t>acquisition_count</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>21.19</v>
+          <t>FY2019</t>
+        </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>millions</t>
+          <t>count</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>third_party</t>
+          <t>unreliable</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.macrotrends.net/stocks/charts/CNSWF/constellation-software/shares-outstanding</t>
+          <t>https://nicoper.substack.com/p/4-constellation-acquisitions-2022</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Matches ledger.json.</t>
+          <t>Third-party count; matches parent_long_run. Set to gap: counts disclosed major deals only, not the annual total.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>shares_outstanding</t>
+          <t>acquisition_count</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2021</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>21.19</v>
+        <v>85</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>millions</t>
+          <t>count approximate, company-wide, stated as a minimum ('more than')</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -6518,12 +6608,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.macrotrends.net/stocks/charts/CNSWF/constellation-software/shares-outstanding</t>
+          <t>https://explore.volarisgroup.com/volaris-group-blog/volaris-recognized-as-a-top-acquirer</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Matches ledger.json.</t>
+          <t>Third-party (Volaris/Corum Group) reporting; not a Constellation-disclosed figure.</t>
         </is>
       </c>
     </row>
@@ -6535,7 +6625,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -6548,17 +6638,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/03/09/3251696/0/en/constellation-software-inc-announces-results-for-the-fourth-quarter-and-year-ended-december-31-2025-and-declares-quarterly-dividend.html</t>
+          <t>https://www.macrotrends.net/stocks/charts/CNSWF/constellation-software/shares-outstanding</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>21,191,530 shares per the company's FY2025 results release.</t>
+          <t>Matches ledger.json.</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6660,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>FY2006</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -6578,7 +6668,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>millions of shares, approximate, carried forward</t>
+          <t>millions</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -6588,12 +6678,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://thequalityinvestor.substack.com/p/constellation-software-180x-in-less</t>
+          <t>https://www.macrotrends.net/stocks/charts/CNSWF/constellation-software/shares-outstanding</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2006. Per share figures for this year rest on this assumption and are labelled approximate.</t>
+          <t>Matches ledger.json.</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6695,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>FY2007</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -6613,22 +6703,22 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>millions of shares, approximate, carried forward</t>
+          <t>millions</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>third_party</t>
+          <t>company</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://thequalityinvestor.substack.com/p/constellation-software-180x-in-less</t>
+          <t>https://www.globenewswire.com/news-release/2026/03/09/3251696/0/en/constellation-software-inc-announces-results-for-the-fourth-quarter-and-year-ended-december-31-2025-and-declares-quarterly-dividend.html</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2007. Per share figures for this year rest on this assumption and are labelled approximate.</t>
+          <t>21,191,530 shares per the company's FY2025 results release.</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6730,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>FY2008</t>
+          <t>FY2006</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -6663,7 +6753,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2008. Per share figures for this year rest on this assumption and are labelled approximate.</t>
+          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2006. Per share figures for this year rest on this assumption and are labelled approximate.</t>
         </is>
       </c>
     </row>
@@ -6675,7 +6765,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>FY2009</t>
+          <t>FY2007</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -6698,7 +6788,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2009. Per share figures for this year rest on this assumption and are labelled approximate.</t>
+          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2007. Per share figures for this year rest on this assumption and are labelled approximate.</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6800,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>FY2010</t>
+          <t>FY2008</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -6733,7 +6823,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2010. Per share figures for this year rest on this assumption and are labelled approximate.</t>
+          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2008. Per share figures for this year rest on this assumption and are labelled approximate.</t>
         </is>
       </c>
     </row>
@@ -6745,7 +6835,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>FY2011</t>
+          <t>FY2009</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -6768,7 +6858,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2011. Per share figures for this year rest on this assumption and are labelled approximate.</t>
+          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2009. Per share figures for this year rest on this assumption and are labelled approximate.</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6870,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>FY2012</t>
+          <t>FY2010</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -6803,7 +6893,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2012. Per share figures for this year rest on this assumption and are labelled approximate.</t>
+          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2010. Per share figures for this year rest on this assumption and are labelled approximate.</t>
         </is>
       </c>
     </row>
@@ -6815,7 +6905,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>FY2013</t>
+          <t>FY2011</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -6838,7 +6928,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2013. Per share figures for this year rest on this assumption and are labelled approximate.</t>
+          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2011. Per share figures for this year rest on this assumption and are labelled approximate.</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6940,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>FY2014</t>
+          <t>FY2012</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -6873,7 +6963,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2014. Per share figures for this year rest on this assumption and are labelled approximate.</t>
+          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2012. Per share figures for this year rest on this assumption and are labelled approximate.</t>
         </is>
       </c>
     </row>
@@ -6885,7 +6975,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>FY2015</t>
+          <t>FY2013</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -6908,7 +6998,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2015. Per share figures for this year rest on this assumption and are labelled approximate.</t>
+          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2013. Per share figures for this year rest on this assumption and are labelled approximate.</t>
         </is>
       </c>
     </row>
@@ -6920,7 +7010,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>FY2016</t>
+          <t>FY2014</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -6943,7 +7033,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2016. Per share figures for this year rest on this assumption and are labelled approximate.</t>
+          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2014. Per share figures for this year rest on this assumption and are labelled approximate.</t>
         </is>
       </c>
     </row>
@@ -6955,7 +7045,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>FY2017</t>
+          <t>FY2015</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -6978,7 +7068,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2017. Per share figures for this year rest on this assumption and are labelled approximate.</t>
+          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2015. Per share figures for this year rest on this assumption and are labelled approximate.</t>
         </is>
       </c>
     </row>
@@ -6990,7 +7080,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>FY2018</t>
+          <t>FY2016</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -7013,7 +7103,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2018. Per share figures for this year rest on this assumption and are labelled approximate.</t>
+          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2016. Per share figures for this year rest on this assumption and are labelled approximate.</t>
         </is>
       </c>
     </row>
@@ -7025,7 +7115,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>FY2019</t>
+          <t>FY2017</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -7048,7 +7138,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2019. Per share figures for this year rest on this assumption and are labelled approximate.</t>
+          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2017. Per share figures for this year rest on this assumption and are labelled approximate.</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7150,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>FY2020</t>
+          <t>FY2018</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -7083,7 +7173,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2020. Per share figures for this year rest on this assumption and are labelled approximate.</t>
+          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2018. Per share figures for this year rest on this assumption and are labelled approximate.</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7185,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2019</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -7118,7 +7208,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2021. Per share figures for this year rest on this assumption and are labelled approximate.</t>
+          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2019. Per share figures for this year rest on this assumption and are labelled approximate.</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7220,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2020</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -7153,62 +7243,62 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2022. Per share figures for this year rest on this assumption and are labelled approximate.</t>
+          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2020. Per share figures for this year rest on this assumption and are labelled approximate.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>dividends_per_share_regular</t>
+          <t>shares_outstanding</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>FY2010</t>
+          <t>FY2021</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>2</v>
+        <v>21.19</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>CAD per share approximate</t>
+          <t>millions of shares, approximate, carried forward</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://www.csisoftware.com/docs/default-source/press-releases/q4_2010_press_release.pdf</t>
+          <t>https://thequalityinvestor.substack.com/p/constellation-software-180x-in-less</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dividend declared March 2, 2011 for FY2010; currency assumed CAD (TSX-listed shares), not directly confirmed from the release text. Whether styled 'annual' or an aggregate of quarterly payments was not confirmed.</t>
+          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2021. Per share figures for this year rest on this assumption and are labelled approximate.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>dividends_per_share_regular</t>
+          <t>shares_outstanding</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>FY2011</t>
+          <t>FY2022</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>2</v>
+        <v>21.19</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>CAD per share approximate</t>
+          <t>millions of shares, approximate, carried forward</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -7218,12 +7308,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://businesscaseweekly.substack.com/p/bcw-49-constellation-software</t>
+          <t>https://thequalityinvestor.substack.com/p/constellation-software-180x-in-less</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>'$2 a share for 2011 in total', before the board adopted a true $1/share quarterly dividend starting Q1 2012.</t>
+          <t>Assumption applied by Fable on 2026-09-14: the source states 21,191,530 shares outstanding, 'mostly unchanged since 2006' and 'has not grown since the IPO'; corroborated by https://www.marketscreener.com/quote/stock/CONSTELLATION-SOFTWARE-IN-1409607/news/Multibagger-Stories-Constellation-Software-44687508/. No company sourced year end count was found for FY2022. Per share figures for this year rest on this assumption and are labelled approximate.</t>
         </is>
       </c>
     </row>
@@ -7235,15 +7325,15 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>FY2013</t>
+          <t>FY2010</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>USD (4 x USD 1.00 quarterly)</t>
+          <t>CAD per share approximate</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -7253,12 +7343,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2013/10/30/1474983/0/en/Constellation-Software-Inc-Announces-Results-for-the-Third-Quarter-Ended-September-30-2013-and-Declares-Quarterly-Dividend.html</t>
+          <t>https://www.csisoftware.com/docs/default-source/press-releases/q4_2010_press_release.pdf</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Quarterly rate of USD 1.00 confirmed; annual total assumes the same rate held for all four quarters of FY2013 (unchanged since 2012 per company disclosure pattern).</t>
+          <t>Dividend declared March 2, 2011 for FY2010; currency assumed CAD (TSX-listed shares), not directly confirmed from the release text. Whether styled 'annual' or an aggregate of quarterly payments was not confirmed.</t>
         </is>
       </c>
     </row>
@@ -7270,28 +7360,32 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>FY2014</t>
+          <t>FY2011</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>USD (4 x USD 1.00 quarterly)</t>
+          <t>CAD per share approximate</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2014/03/06/1475011/0/en/Constellation-Software-Inc-Declares-Quarterly-Dividend.html</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr"/>
+          <t>https://businesscaseweekly.substack.com/p/bcw-49-constellation-software</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>'$2 a share for 2011 in total', before the board adopted a true $1/share quarterly dividend starting Q1 2012.</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7301,7 +7395,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>FY2015</t>
+          <t>FY2013</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -7319,12 +7413,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2016/02/17/1061530/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2015-and-Declares-Quarterly-Dividend.html</t>
+          <t>https://www.globenewswire.com/news-release/2013/10/30/1474983/0/en/Constellation-Software-Inc-Announces-Results-for-the-Third-Quarter-Ended-September-30-2013-and-Declares-Quarterly-Dividend.html</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>No special dividend named in this release for FY2015.</t>
+          <t>Quarterly rate of USD 1.00 confirmed; annual total assumes the same rate held for all four quarters of FY2013 (unchanged since 2012 per company disclosure pattern).</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7430,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>FY2018</t>
+          <t>FY2014</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -7354,14 +7448,10 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2019/02/14/1725078/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2018-and-Declares-Quarterly-and-Special-Dividends.html</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>Declared alongside the USD 20.00 special dividend.</t>
-        </is>
-      </c>
+          <t>https://www.globenewswire.com/news-release/2014/03/06/1475011/0/en/Constellation-Software-Inc-Declares-Quarterly-Dividend.html</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7371,7 +7461,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>FY2019</t>
+          <t>FY2015</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -7389,10 +7479,14 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2020/02/13/1984977/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2019-and-Declares-Quarterly-Dividend.html</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr"/>
+          <t>https://www.globenewswire.com/news-release/2016/02/17/1061530/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2015-and-Declares-Quarterly-Dividend.html</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>No special dividend named in this release for FY2015.</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7402,7 +7496,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>FY2020</t>
+          <t>FY2018</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -7420,10 +7514,14 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2020/11/02/2118890/0/en/Constellation-Software-Inc-Announces-Results-for-the-Third-Quarter-Ended-September-30-2020-and-Declares-Quarterly-Dividend.html</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr"/>
+          <t>https://www.globenewswire.com/news-release/2019/02/14/1725078/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2018-and-Declares-Quarterly-and-Special-Dividends.html</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Declared alongside the USD 20.00 special dividend.</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7433,7 +7531,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2019</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -7451,14 +7549,10 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2023/03/29/2637195/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2022-and-Declares-Quarterly-Dividend.html</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>No special dividend named in this release.</t>
-        </is>
-      </c>
+          <t>https://www.globenewswire.com/news-release/2020/02/13/1984977/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2019-and-Declares-Quarterly-Dividend.html</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7468,7 +7562,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2020</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -7486,7 +7580,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2024/3/6/2841834/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2023-and-Declares-Quarterly-Dividend.html</t>
+          <t>https://www.globenewswire.com/news-release/2020/11/02/2118890/0/en/Constellation-Software-Inc-Announces-Results-for-the-Third-Quarter-Ended-September-30-2020-and-Declares-Quarterly-Dividend.html</t>
         </is>
       </c>
       <c r="G172" t="inlineStr"/>
@@ -7499,7 +7593,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2022</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -7517,10 +7611,14 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2025/03/07/3039269/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2024-and-Declares-Quarterly-Dividend.html</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr"/>
+          <t>https://www.globenewswire.com/news-release/2023/03/29/2637195/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2022-and-Declares-Quarterly-Dividend.html</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>No special dividend named in this release.</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7530,7 +7628,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -7548,32 +7646,28 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2026/03/09/3251696/0/en/constellation-software-inc-announces-results-for-the-fourth-quarter-and-year-ended-december-31-2025-and-declares-quarterly-dividend.html</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>Regular rate still USD 1.00 quarterly; no special dividend named.</t>
-        </is>
-      </c>
+          <t>https://www.globenewswire.com/news-release/2024/3/6/2841834/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2023-and-Declares-Quarterly-Dividend.html</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>dividends_per_share_special</t>
+          <t>dividends_per_share_regular</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>FY2018</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>USD per share, one-time special dividend</t>
+          <t>USD (4 x USD 1.00 quarterly)</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -7583,32 +7677,28 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2019/02/14/1725078/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2018-and-Declares-Quarterly-and-Special-Dividends.html</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Declared February 14, 2019 alongside FY2018 results and the regular USD 1.00 quarterly dividend, both paid April 5, 2019 to holders of record March 16, 2019. Company: 'we have capital in excess of our needs and should return the excess to shareholders.' Known issue 8: this is the only special dividend found anywhere across all five stage1 sweeps; earlier years were specifically searched and none were found -- see coverage note.</t>
-        </is>
-      </c>
+          <t>https://www.globenewswire.com/news-release/2025/03/07/3039269/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2024-and-Declares-Quarterly-Dividend.html</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>employees</t>
+          <t>dividends_per_share_regular</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>FY2011</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1022</v>
+        <v>4</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>count (R&amp;D employees only, NOT total company headcount)</t>
+          <t>USD (4 x USD 1.00 quarterly)</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -7618,177 +7708,189 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>https://www.csisoftware.com/docs/default-source/investor-relations/statutory-filings/csu-2011-aif.pdf</t>
+          <t>https://www.globenewswire.com/news-release/2026/03/09/3251696/0/en/constellation-software-inc-announces-results-for-the-fourth-quarter-and-year-ended-december-31-2025-and-declares-quarterly-dividend.html</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2011 AIF: ~1,022 employees involved in R&amp;D for fiscal 2011. This is an R&amp;D headcount subset; no total company-wide employee figure was found for FY2011.</t>
+          <t>Regular rate still USD 1.00 quarterly; no special dividend named.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>employees</t>
+          <t>dividends_per_share_regular</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>FY2015</t>
+          <t>FY2012</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>9924</v>
+        <v>4</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>average full-time employees (annual average)</t>
+          <t>USD (4 x USD 1.00 quarterly), derived</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>https://www.csisoftware.com/wp-content/uploads/2026/04/2015-annual-information-form-final.pdf</t>
+          <t>https://www.globenewswire.com/news-release/2019/02/14/1725078/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2018-and-Declares-Quarterly-and-Special-Dividends.html</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2015 AIF: ~9,924 FTE average for fiscal 2015. A point-in-time figure of ~10,478 as at Dec 31, 2015 is also in the same source (different measurement basis, not a conflict).</t>
+          <t>Not individually sourced for FY2012. The quarterly rate of USD 1.00 is company sourced for FY2013 to FY2015 and FY2018 to FY2020 and FY2022 to FY2025 with no change announced; carried as 4.00 for FY2012 by Fable review 2026-09-14 and labelled derived.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>employees</t>
+          <t>dividends_per_share_regular</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>FY2019</t>
+          <t>FY2016</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>23000</v>
+        <v>4</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>approximate full-time employees, as at Dec 31 2019</t>
+          <t>USD (4 x USD 1.00 quarterly), derived</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>https://www.csisoftware.com/docs/default-source/investor-relations/statutory-filings/2019-annual-information-form---final.pdf</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr"/>
+          <t>https://www.globenewswire.com/news-release/2019/02/14/1725078/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2018-and-Declares-Quarterly-and-Special-Dividends.html</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Not individually sourced for FY2016. The quarterly rate of USD 1.00 is company sourced for FY2013 to FY2015 and FY2018 to FY2020 and FY2022 to FY2025 with no change announced; carried as 4.00 for FY2016 by Fable review 2026-09-14 and labelled derived.</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>employees</t>
+          <t>dividends_per_share_regular</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2017</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>41000</v>
+        <v>4</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>approximate full-time employees, globally</t>
+          <t>USD (4 x USD 1.00 quarterly), derived</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>https://www.csisoftware.com/docs/default-source/investor-relations/2022-agm/csi-2021-mic-en.pdf</t>
+          <t>https://www.globenewswire.com/news-release/2019/02/14/1725078/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2018-and-Declares-Quarterly-and-Special-Dividends.html</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Known issue 7: company AIF-sourced figure of ~41,000 preferred over a third-party (macrotrends) figure of 45,000 as at Dec 31, 2022, which is recorded as a conflict.</t>
+          <t>Not individually sourced for FY2017. The quarterly rate of USD 1.00 is company sourced for FY2013 to FY2015 and FY2018 to FY2020 and FY2022 to FY2025 with no change announced; carried as 4.00 for FY2017 by Fable review 2026-09-14 and labelled derived.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>employees</t>
+          <t>dividends_per_share_regular</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2021</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>57637</v>
+        <v>4</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>count, approximate (workforce-analytics estimate, not company-disclosed)</t>
+          <t>USD (4 x USD 1.00 quarterly), derived</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>third_party</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>https://www.reveliolabs.com/companies/constellation-software/employees/</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr"/>
+          <t>https://www.globenewswire.com/news-release/2019/02/14/1725078/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2018-and-Declares-Quarterly-and-Special-Dividends.html</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Not individually sourced for FY2021. The quarterly rate of USD 1.00 is company sourced for FY2013 to FY2015 and FY2018 to FY2020 and FY2022 to FY2025 with no change announced; carried as 4.00 for FY2021 by Fable review 2026-09-14 and labelled derived.</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>employees</t>
+          <t>dividends_per_share_special</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2018</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>57217</v>
+        <v>20</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>count, approximate (workforce-analytics estimate, not company-disclosed)</t>
+          <t>USD per share, one-time special dividend</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>third_party</t>
+          <t>company</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>https://www.reveliolabs.com/companies/constellation-software/employees/</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr"/>
+          <t>https://www.globenewswire.com/news-release/2019/02/14/1725078/0/en/Constellation-Software-Inc-Announces-Results-for-the-Fourth-Quarter-and-Year-Ended-December-31-2018-and-Declares-Quarterly-and-Special-Dividends.html</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Declared February 14, 2019 alongside FY2018 results and the regular USD 1.00 quarterly dividend, both paid April 5, 2019 to holders of record March 16, 2019. Company: 'we have capital in excess of our needs and should return the excess to shareholders.' Known issue 8: this is the only special dividend found anywhere across all five stage1 sweeps; earlier years were specifically searched and none were found -- see coverage note.</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7798,50 +7900,50 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2011</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>55775</v>
+        <v>1022</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>count, approximate (workforce-analytics estimate, not company-disclosed)</t>
+          <t>count (R&amp;D employees only, NOT total company headcount)</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>third_party</t>
+          <t>company</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>https://www.reveliolabs.com/companies/constellation-software/employees/</t>
+          <t>https://www.csisoftware.com/docs/default-source/investor-relations/statutory-filings/csu-2011-aif.pdf</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Down 2.6%/-1,442 from FY2024 per the same aggregator.</t>
+          <t>2011 AIF: ~1,022 employees involved in R&amp;D for fiscal 2011. This is an R&amp;D headcount subset; no total company-wide employee figure was found for FY2011.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>roic_pct</t>
+          <t>employees</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>FY2009</t>
+          <t>FY2015</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>24</v>
+        <v>9924</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>average full-time employees (annual average)</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -7851,32 +7953,32 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>https://www.csisoftware.com/docs/default-source/investor-relations/presidents-letter/shareholder-letter---2009.pdf</t>
+          <t>https://www.csisoftware.com/wp-content/uploads/2026/04/2015-annual-information-form-final.pdf</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2009 President's letter reported 24% ROIC for 2009.</t>
+          <t>2015 AIF: ~9,924 FTE average for fiscal 2015. A point-in-time figure of ~10,478 as at Dec 31, 2015 is also in the same source (different measurement basis, not a conflict).</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>roic_pct</t>
+          <t>employees</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>FY2010</t>
+          <t>FY2019</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>25</v>
+        <v>23000</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>approximate full-time employees, as at Dec 31 2019</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -7886,54 +7988,50 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>https://www.csisoftware.com/docs/default-source/investor-relations/presidents-letter/shareholder-letter---2010.pdf</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>Reused from long-term-hold/holdings.json parent_long_run.</t>
-        </is>
-      </c>
+          <t>https://www.csisoftware.com/docs/default-source/investor-relations/statutory-filings/2019-annual-information-form---final.pdf</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>roic_plus_organic_pct</t>
+          <t>employees</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>FY2017</t>
+          <t>FY2022</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>33</v>
+        <v>41000</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>percent, approximate</t>
+          <t>approximate full-time employees, globally</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>third_party</t>
+          <t>company</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>https://uploads-ssl.webflow.com/60e3655ca778911eb64b2a00/60f0777ead89beba9c51c0b3_Constellation-Software-Inc.-Shareholder-Letters.pdf</t>
+          <t>https://www.csisoftware.com/docs/default-source/investor-relations/2022-agm/csi-2021-mic-en.pdf</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>ROIC+OGr 'remained relatively flat at 33%' in 2017 with shareholders' Average Invested Capital growing 29%. Corroborated by a second third-party source (bizalmanac.substack.com) citing the same 33% figure and 29% ROIC alone for FY2017.</t>
+          <t>Known issue 7: company AIF-sourced figure of ~41,000 preferred over a third-party (macrotrends) figure of 45,000 as at Dec 31, 2022, which is recorded as a conflict.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>capex</t>
+          <t>employees</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -7942,11 +8040,11 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>68</v>
+        <v>57637</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>USD millions, approximate</t>
+          <t>count, approximate (workforce-analytics estimate, not company-disclosed)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -7956,19 +8054,15 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>https://www.stockopedia.com/share-prices/constellation-software-TSE:CSU/cashflow/</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>Aggregator-derived cash-flow-statement figure; not located in a company press release.</t>
-        </is>
-      </c>
+          <t>https://www.reveliolabs.com/companies/constellation-software/employees/</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>capex</t>
+          <t>employees</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -7977,11 +8071,11 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>72</v>
+        <v>57217</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>USD millions, approximate</t>
+          <t>count, approximate (workforce-analytics estimate, not company-disclosed)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -7991,32 +8085,28 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>https://www.stockopedia.com/share-prices/constellation-software-TSE:CSU/cashflow/</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>Aggregator-derived cash-flow-statement figure; not located in a company press release.</t>
-        </is>
-      </c>
+          <t>https://www.reveliolabs.com/companies/constellation-software/employees/</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>share_price_cad_year_end</t>
+          <t>employees</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>IPO 2006-05-17</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>17</v>
+        <v>55775</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>CAD, IPO offering price (not a fiscal year-end close)</t>
+          <t>count, approximate (workforce-analytics estimate, not company-disclosed)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -8026,94 +8116,102 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>https://www.cantechletter.com/2025/05/constellation-software-has-delivered-a-36000-return-since-its-ipo-is-it-still-a-buy/</t>
+          <t>https://www.reveliolabs.com/companies/constellation-software/employees/</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Constellation listed on the TSX May 17, 2006 at an IPO price of C$17.00/share (first-day close C$18.30). Not independently confirmed from Constellation's own short-form prospectus (WebFetch unavailable); treated as third_party. No FY2006-FY2025 fiscal year-end closing price could be sourced via WebSearch in any of the five intake sweeps -- year end prices are gap for every one of the 19 fiscal years, per known issue 9.</t>
+          <t>Down 2.6%/-1,442 from FY2024 per the same aggregator.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>aggregate_returns</t>
+          <t>roic_pct</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>total_return_10yr_pct</t>
+          <t>FY2009</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>460.73</v>
+        <v>24</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>percent total return, CNSWF USD, approximate, 10 years to 2026-05</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>third_party</t>
+          <t>company</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>https://www.financecharts.com/stocks/CNSWF/performance/total-return-cagr</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr"/>
+          <t>https://www.csisoftware.com/docs/default-source/investor-relations/presidents-letter/shareholder-letter---2009.pdf</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>2009 President's letter reported 24% ROIC for 2009.</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>aggregate_returns</t>
+          <t>roic_pct</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>total_return_15yr_pct</t>
+          <t>FY2010</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>3597.83</v>
+        <v>25</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>percent total return, CNSWF USD, approximate, 15 years to 2026-05</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>third_party</t>
+          <t>company</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>https://www.financecharts.com/stocks/CNSWF/performance/total-return-cagr</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr"/>
+          <t>https://www.csisoftware.com/docs/default-source/investor-relations/presidents-letter/shareholder-letter---2010.pdf</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Reused from long-term-hold/holdings.json parent_long_run.</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>aggregate_returns</t>
+          <t>roic_plus_organic_pct</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>annualized_return_10yr_pct</t>
+          <t>FY2017</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>19.63</v>
+        <v>33</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>percent per year, CSU.TO CAD, approximate, 10 years to 2026-09</t>
+          <t>percent, approximate</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -8123,45 +8221,247 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>https://portfolioslab.com/symbol/CSU.TO</t>
+          <t>https://uploads-ssl.webflow.com/60e3655ca778911eb64b2a00/60f0777ead89beba9c51c0b3_Constellation-Software-Inc.-Shareholder-Letters.pdf</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>S&amp;P 500 averaged 13.95 percent over the same window per the same source.</t>
+          <t>ROIC+OGr 'remained relatively flat at 33%' in 2017 with shareholders' Average Invested Capital growing 29%. Corroborated by a second third-party source (bizalmanac.substack.com) citing the same 33% figure and 29% ROIC alone for FY2017.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>68</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>USD millions, approximate</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>third_party</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>https://www.stockopedia.com/share-prices/constellation-software-TSE:CSU/cashflow/</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Aggregator-derived cash-flow-statement figure; not located in a company press release.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>72</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>USD millions, approximate</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>third_party</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>https://www.stockopedia.com/share-prices/constellation-software-TSE:CSU/cashflow/</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Aggregator-derived cash-flow-statement figure; not located in a company press release.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>share_price_cad_year_end</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>IPO 2006-05-17</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>17</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>CAD, IPO offering price (not a fiscal year-end close)</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>third_party</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>https://www.cantechletter.com/2025/05/constellation-software-has-delivered-a-36000-return-since-its-ipo-is-it-still-a-buy/</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Constellation listed on the TSX May 17, 2006 at an IPO price of C$17.00/share (first-day close C$18.30). Not independently confirmed from Constellation's own short-form prospectus (WebFetch unavailable); treated as third_party. No FY2006-FY2025 fiscal year-end closing price could be sourced via WebSearch in any of the five intake sweeps -- year end prices are gap for every one of the 19 fiscal years, per known issue 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
           <t>aggregate_returns</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>total_return_10yr_pct</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>460.73</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>percent total return, CNSWF USD, approximate, 10 years to 2026-05</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>third_party</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>https://www.financecharts.com/stocks/CNSWF/performance/total-return-cagr</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>aggregate_returns</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>total_return_15yr_pct</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>3597.83</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>percent total return, CNSWF USD, approximate, 15 years to 2026-05</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>third_party</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>https://www.financecharts.com/stocks/CNSWF/performance/total-return-cagr</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>aggregate_returns</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>annualized_return_10yr_pct</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>percent per year, CSU.TO CAD, approximate, 10 years to 2026-09</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>third_party</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>https://portfolioslab.com/symbol/CSU.TO</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 averaged 13.95 percent over the same window per the same source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>aggregate_returns</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
         <is>
           <t>positive_years_count</t>
         </is>
       </c>
-      <c r="C192" t="n">
+      <c r="C198" t="n">
         <v>17</v>
       </c>
-      <c r="D192" t="inlineStr">
+      <c r="D198" t="inlineStr">
         <is>
           <t>positive calendar years out of since-listing total (2 negative), approximate</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
+      <c r="E198" t="inlineStr">
         <is>
           <t>third_party</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr">
+      <c r="F198" t="inlineStr">
         <is>
           <t>https://portfolioslab.com/symbol/CSU.TO</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8313,13 +8613,13 @@
         <v>2.2</v>
       </c>
       <c r="J3" t="n">
-        <v>116.73</v>
+        <v>96.62</v>
       </c>
       <c r="K3" t="n">
         <v>1099.9</v>
       </c>
       <c r="L3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -8358,7 +8658,7 @@
         <v>2807</v>
       </c>
       <c r="L4" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -8375,12 +8675,18 @@
       <c r="C5" t="n">
         <v>20.63</v>
       </c>
+      <c r="D5" t="n">
+        <v>28.19</v>
+      </c>
       <c r="E5" t="n">
         <v>25.42</v>
       </c>
       <c r="F5" t="n">
         <v>20.63</v>
       </c>
+      <c r="G5" t="n">
+        <v>28.19</v>
+      </c>
       <c r="H5" t="n">
         <v>25.42</v>
       </c>
@@ -8388,7 +8694,7 @@
         <v>2.5</v>
       </c>
       <c r="J5" t="n">
-        <v>60.18</v>
+        <v>75.98</v>
       </c>
       <c r="K5" t="n">
         <v>5703</v>
@@ -8418,13 +8724,13 @@
         <v>0.76</v>
       </c>
       <c r="J6" t="n">
-        <v>83.7</v>
+        <v>83.05</v>
       </c>
       <c r="K6" t="n">
         <v>9703.9</v>
       </c>
       <c r="L6" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -9142,14 +9448,14 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
         <v>6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>revenue, net_income_attributable, acquisitions_cash_spent, organic_growth_pct, cash_metric (adjusted_net_income)</t>
+          <t>revenue, net_income_attributable, cash_from_operations, acquisitions_cash_spent, organic_growth_pct, cash_metric (adjusted_net_income)</t>
         </is>
       </c>
     </row>
@@ -9250,14 +9556,14 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
         <v>6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>revenue, net_income_attributable, acquisitions_cash_spent, organic_growth_pct, cash_metric (fcfa2s)</t>
+          <t>revenue, net_income_attributable, cash_from_operations, acquisitions_cash_spent, organic_growth_pct, cash_metric (fcfa2s)</t>
         </is>
       </c>
     </row>

--- a/analysis/constellation-software/history-2007-2025/history_metrics.xlsx
+++ b/analysis/constellation-software/history-2007-2025/history_metrics.xlsx
@@ -8645,9 +8645,6 @@
       <c r="G4" t="n">
         <v>25.26</v>
       </c>
-      <c r="H4" t="n">
-        <v>17.52</v>
-      </c>
       <c r="I4" t="n">
         <v>1.8</v>
       </c>
